--- a/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
+++ b/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
@@ -15,7 +15,11 @@
     <sheet name="DisputeTracker" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="BranchFacts" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="MatFacts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SourceHistoricalDisputes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Meetings" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="RepsRecruited" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Snapshots" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SchoolGeo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SourceHistoricalDisputes" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,40 +153,111 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SourceGIAS" displayName="SourceGIAS" ref="A1:G3" headerRowCount="1">
-  <autoFilter ref="A1:G3"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SourceGIAS" displayName="SourceGIAS" ref="A1:Q2" headerRowCount="1">
+  <autoFilter ref="A1:Q2"/>
+  <tableColumns count="17">
     <tableColumn id="1" name="URN"/>
     <tableColumn id="2" name="School name"/>
-    <tableColumn id="3" name="Phase"/>
-    <tableColumn id="4" name="LA (borough)"/>
-    <tableColumn id="5" name="Establishment status"/>
-    <tableColumn id="6" name="Trusts (MAT)"/>
-    <tableColumn id="7" name="Postcode"/>
+    <tableColumn id="3" name="Type of establishment"/>
+    <tableColumn id="4" name="Phase"/>
+    <tableColumn id="5" name="LA (borough)"/>
+    <tableColumn id="6" name="Establishment status"/>
+    <tableColumn id="7" name="Religious character"/>
+    <tableColumn id="8" name="Diocese"/>
+    <tableColumn id="9" name="Trusts (MAT)"/>
+    <tableColumn id="10" name="School sponsors"/>
+    <tableColumn id="11" name="Federations"/>
+    <tableColumn id="12" name="Postcode"/>
+    <tableColumn id="13" name="School website"/>
+    <tableColumn id="14" name="Telephone"/>
+    <tableColumn id="15" name="Head title"/>
+    <tableColumn id="16" name="Head first name"/>
+    <tableColumn id="17" name="Head last name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceWorkforce" displayName="SourceWorkforce" ref="A1:G3" headerRowCount="1">
-  <autoFilter ref="A1:G3"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="URN"/>
-    <tableColumn id="2" name="Workforce headcount"/>
-    <tableColumn id="3" name="All teachers"/>
-    <tableColumn id="4" name="Classroom teachers"/>
-    <tableColumn id="5" name="Leadership teachers"/>
-    <tableColumn id="6" name="All support staff"/>
-    <tableColumn id="7" name="Teaching assistants"/>
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="RepsRecruited" displayName="RepsRecruited" ref="A1:D2" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="URN"/>
+    <tableColumn id="4" name="Logged by"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Snapshots" displayName="Snapshots" ref="A1:H2" headerRowCount="1">
+  <autoFilter ref="A1:H2"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Snapshot date"/>
+    <tableColumn id="2" name="URN"/>
+    <tableColumn id="3" name="Overall members"/>
+    <tableColumn id="4" name="Rep count"/>
+    <tableColumn id="5" name="Workforce headcount"/>
+    <tableColumn id="6" name="Voted"/>
+    <tableColumn id="7" name="Volunteers"/>
+    <tableColumn id="8" name="WP conversations"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="SchoolGeo" displayName="SchoolGeo" ref="A1:D2" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="URN"/>
+    <tableColumn id="2" name="Latitude"/>
+    <tableColumn id="3" name="Longitude"/>
+    <tableColumn id="4" name="Geocoded date"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="SourceHistoricalDisputes" displayName="SourceHistoricalDisputes" ref="A1:F2" headerRowCount="1">
+  <autoFilter ref="A1:F2"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="School year"/>
+    <tableColumn id="2" name="Employer/school"/>
+    <tableColumn id="3" name="Branch"/>
+    <tableColumn id="4" name="RO/SRO responsible"/>
+    <tableColumn id="5" name="Ballot summary"/>
+    <tableColumn id="6" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceWorkforce" displayName="SourceWorkforce" ref="A1:J2" headerRowCount="1">
+  <autoFilter ref="A1:J2"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="URN"/>
+    <tableColumn id="2" name="School name"/>
+    <tableColumn id="3" name="LA (borough)"/>
+    <tableColumn id="4" name="School type"/>
+    <tableColumn id="5" name="Workforce headcount"/>
+    <tableColumn id="6" name="All teachers"/>
+    <tableColumn id="7" name="Classroom teachers"/>
+    <tableColumn id="8" name="Leadership teachers"/>
+    <tableColumn id="9" name="All support staff"/>
+    <tableColumn id="10" name="Teaching assistants"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WCtoURN" displayName="WCtoURN" ref="A1:B3" headerRowCount="1">
-  <autoFilter ref="A1:B3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WCtoURN" displayName="WCtoURN" ref="A1:B2" headerRowCount="1">
+  <autoFilter ref="A1:B2"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Workplace code"/>
     <tableColumn id="2" name="URN"/>
@@ -192,20 +267,31 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourceNEUDashboard" displayName="SourceNEUDashboard" ref="A1:K3" headerRowCount="1">
-  <autoFilter ref="A1:K3"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourceNEUDashboard" displayName="SourceNEUDashboard" ref="A1:V2" headerRowCount="1">
+  <autoFilter ref="A1:V2"/>
+  <tableColumns count="22">
     <tableColumn id="1" name="Workplace code"/>
-    <tableColumn id="2" name="Overall members"/>
-    <tableColumn id="3" name="Voted"/>
-    <tableColumn id="4" name="Rep count"/>
-    <tableColumn id="5" name="Volunteers"/>
-    <tableColumn id="6" name="WP conversations"/>
-    <tableColumn id="7" name="2025 indicative voted"/>
-    <tableColumn id="8" name="2024 indicative voted"/>
-    <tableColumn id="9" name="Hold a meeting"/>
-    <tableColumn id="10" name="Needs support"/>
-    <tableColumn id="11" name="Pledged to vote"/>
+    <tableColumn id="2" name="Workplace name"/>
+    <tableColumn id="3" name="Overall members"/>
+    <tableColumn id="4" name="Voted"/>
+    <tableColumn id="5" name="Turnout"/>
+    <tableColumn id="6" name="Rep count"/>
+    <tableColumn id="7" name="Branch name"/>
+    <tableColumn id="8" name="District name"/>
+    <tableColumn id="9" name="Region name"/>
+    <tableColumn id="10" name="Volunteers"/>
+    <tableColumn id="11" name="WP conversations"/>
+    <tableColumn id="12" name="Rep recruited volunteer"/>
+    <tableColumn id="13" name="Joined community"/>
+    <tableColumn id="14" name="Completed activate action"/>
+    <tableColumn id="15" name="Agreed to briefing"/>
+    <tableColumn id="16" name="2025 indicative voted"/>
+    <tableColumn id="17" name="2024 indicative voted"/>
+    <tableColumn id="18" name="Hold a meeting"/>
+    <tableColumn id="19" name="Needs support"/>
+    <tableColumn id="20" name="Pledged to vote"/>
+    <tableColumn id="21" name="Active SEVs"/>
+    <tableColumn id="22" name="Import date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -253,13 +339,12 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="BranchFacts" displayName="BranchFacts" ref="A1:D33" headerRowCount="1">
-  <autoFilter ref="A1:D33"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="BranchFacts" displayName="BranchFacts" ref="A1:C33" headerRowCount="1">
+  <autoFilter ref="A1:C33"/>
+  <tableColumns count="3">
     <tableColumn id="1" name="Branch"/>
     <tableColumn id="2" name="Is project branch?"/>
-    <tableColumn id="3" name="School meetings held"/>
-    <tableColumn id="4" name="Reps trained since start"/>
+    <tableColumn id="3" name="Reps trained since start"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -278,15 +363,13 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SourceHistoricalDisputes" displayName="SourceHistoricalDisputes" ref="A1:F2" headerRowCount="1">
-  <autoFilter ref="A1:F2"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="School year"/>
-    <tableColumn id="2" name="Employer/school"/>
-    <tableColumn id="3" name="Branch"/>
-    <tableColumn id="4" name="RO/SRO responsible"/>
-    <tableColumn id="5" name="Ballot summary"/>
-    <tableColumn id="6" name="Notes"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Meetings" displayName="Meetings" ref="A1:D2" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="URN"/>
+    <tableColumn id="4" name="Logged by"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -581,16 +664,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,27 +699,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Type of establishment</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LA (borough)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Establishment status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Religious character</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Diocese</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Trusts (MAT)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>School sponsors</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Federations</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Postcode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>School website</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Telephone</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Head title</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Head first name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Head last name</t>
         </is>
       </c>
     </row>
@@ -641,63 +784,70 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>LA nursery school</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>Nursery</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Greenwich</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Does not apply</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>SE8 3EH</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>100098</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE Pound Park Nursery School</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Nursery</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Greenwich</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE MAT</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>SE7 8AF</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>www.example.sch.uk</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>020 7946 0000</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Ms</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Note: Paste your DfE GIAS export here (https://get-information-schools.service.gov.uk/). Not edited by the app.</t>
         </is>
@@ -711,22 +861,365 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>URN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Logged by</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>100097</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Organiser</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Append-only log of reps recruited, written one-click by the app. Distinct from reps TRAINED, which is still a manual figure on BranchFacts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Snapshot date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URN</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Overall members</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rep count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Workforce headcount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Voted</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Volunteers</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WP conversations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>100097</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Append-only weekly capture, written automatically by the app. NEVER edit or delete past rows — this is the only record of how things looked at the time, and it cannot be reconstructed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>URN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Geocoded date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>100097</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>51.481</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>-0.0261</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Cached postcode-&gt;coordinates lookups for the map view. Populated once by the app; safe to delete rows to force a re-lookup.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>School year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Employer/school</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RO/SRO responsible</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ballot summary</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE School</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Harrow</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Officer</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>56% turnout, 43% Yes</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Kept for institutional memory — not read by the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Reference only, not read by the app or kept up to date automatically.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -737,30 +1230,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>School name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LA (borough)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>School type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Workforce headcount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>All teachers</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Classroom teachers</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Leadership teachers</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>All support staff</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Teaching assistants</t>
         </is>
@@ -770,50 +1278,42 @@
       <c r="A2" s="2" t="n">
         <v>100097</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Rachel McMillan Nursery School</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Greenwich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>LA maintained nursery</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>100098</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Note: Paste your DfE School Workforce Census export here. Not edited by the app.</t>
         </is>
@@ -833,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -862,18 +1362,8 @@
         <v>100097</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>WP041624</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>100098</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Note: Maps NEU workplace codes to DfE URNs. Not edited by the app.</t>
         </is>
@@ -893,20 +1383,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -917,52 +1418,107 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Workplace name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Overall members</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Voted</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Turnout</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Rep count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Branch name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>District name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Region name</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Volunteers</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>WP conversations</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Rep recruited volunteer</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Joined community</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Completed activate action</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Agreed to briefing</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>2025 indicative voted</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>2024 indicative voted</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Hold a meeting</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Needs support</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pledged to vote</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Active SEVs</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Import date</t>
         </is>
       </c>
     </row>
@@ -972,76 +1528,82 @@
           <t>WP020292</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Rachel McMillan Nursery School</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Greenwich State Education</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greenwich</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="n">
+      <c r="S2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>WP041624</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Note: Paste your NEU membership/organising system export here. Not edited by the app.</t>
         </is>
@@ -1407,13 +1969,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1429,11 +1990,6 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>School meetings held</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Reps trained since start</t>
         </is>
       </c>
@@ -1452,9 +2008,6 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1470,9 +2023,6 @@
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1488,9 +2038,6 @@
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1506,9 +2053,6 @@
       <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1524,9 +2068,6 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1542,9 +2083,6 @@
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1560,9 +2098,6 @@
       <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1578,9 +2113,6 @@
       <c r="C9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1596,9 +2128,6 @@
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1614,9 +2143,6 @@
       <c r="C11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1632,9 +2158,6 @@
       <c r="C12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1650,9 +2173,6 @@
       <c r="C13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1668,9 +2188,6 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1686,9 +2203,6 @@
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1704,9 +2218,6 @@
       <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1722,9 +2233,6 @@
       <c r="C17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1740,9 +2248,6 @@
       <c r="C18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1758,9 +2263,6 @@
       <c r="C19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1776,9 +2278,6 @@
       <c r="C20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1794,9 +2293,6 @@
       <c r="C21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1812,9 +2308,6 @@
       <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1830,9 +2323,6 @@
       <c r="C23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1848,9 +2338,6 @@
       <c r="C24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1866,9 +2353,6 @@
       <c r="C25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1884,9 +2368,6 @@
       <c r="C26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1902,9 +2383,6 @@
       <c r="C27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1920,9 +2398,6 @@
       <c r="C28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1938,9 +2413,6 @@
       <c r="C29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1956,9 +2428,6 @@
       <c r="C30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1974,9 +2443,6 @@
       <c r="C31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1992,9 +2458,6 @@
       <c r="C32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2010,14 +2473,11 @@
       <c r="C33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Note: One row per London borough/branch. isProjectBranch controls whether it counts toward the dashboard's headline KPIs. Edit directly in Excel.</t>
+          <t>Note: One row per London borough/branch. 'Is project branch?' controls whether it counts toward the dashboard's headline KPIs. School meetings are no longer counted here — they come from the Meetings table.</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2545,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Add a row per MAT you're tracking. Edit directly in Excel — add a row whenever a new MAT enters the project.</t>
+          <t>Note: Add a row per MAT you're tracking. Edit directly in Excel whenever a new MAT enters the project.</t>
         </is>
       </c>
     </row>
@@ -2111,85 +2571,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>School year</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Employer/school</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>URN</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RO/SRO responsible</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Ballot summary</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Logged by</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2022-23</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE School</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Harrow</t>
-        </is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>100097</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE Officer</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>56% turnout, 43% Yes</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Kept for institutional memory — not read by the app.</t>
+          <t>EXAMPLE Organiser</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Reference only, not read by the app or kept up to date automatically.</t>
+          <t>Note: Append-only log of school meetings, written one-click by the app. Branch and project meeting counts are derived from this — do not keep a separate tally.</t>
         </is>
       </c>
     </row>

--- a/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
+++ b/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
@@ -179,13 +179,14 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="RepsRecruited" displayName="RepsRecruited" ref="A1:D2" headerRowCount="1">
-  <autoFilter ref="A1:D2"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="RepsRecruited" displayName="RepsRecruited" ref="A1:E2" headerRowCount="1">
+  <autoFilter ref="A1:E2"/>
+  <tableColumns count="5">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
     <tableColumn id="3" name="URN"/>
-    <tableColumn id="4" name="Logged by"/>
+    <tableColumn id="4" name="Rep name"/>
+    <tableColumn id="5" name="Logged by"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -867,13 +868,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -894,6 +896,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Rep name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Logged by</t>
         </is>
       </c>
@@ -913,6 +920,11 @@
         <v>100097</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Rep</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>EXAMPLE Organiser</t>
         </is>

--- a/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
+++ b/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SourceGIAS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SourceWorkforce" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="WCtoURN" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SourceNEUDashboard" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FieldNotes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DisputeTracker" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="BranchFacts" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MatFacts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Meetings" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="RepsRecruited" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Snapshots" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="SchoolGeo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="SourceHistoricalDisputes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceGIAS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceStratum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourcePayDashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceWorkforceSurvey" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCtoURN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MatAliases" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldNotes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DisputeTracker" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BranchFacts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MatFacts" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meetings" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RepsRecruited" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshots" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchoolGeo" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -179,7 +181,32 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="RepsRecruited" displayName="RepsRecruited" ref="A1:E2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="MatFacts" displayName="MatFacts" ref="A1:C6" headerRowCount="1">
+  <autoFilter ref="A1:C6"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="MAT"/>
+    <tableColumn id="2" name="Is target MAT?"/>
+    <tableColumn id="3" name="Rep committee exists?"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Meetings" displayName="Meetings" ref="A1:D2" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="URN"/>
+    <tableColumn id="4" name="Logged by"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="RepsRecruited" displayName="RepsRecruited" ref="A1:E2" headerRowCount="1">
   <autoFilter ref="A1:E2"/>
   <tableColumns count="5">
     <tableColumn id="1" name="ID"/>
@@ -192,25 +219,45 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Snapshots" displayName="Snapshots" ref="A1:H2" headerRowCount="1">
-  <autoFilter ref="A1:H2"/>
-  <tableColumns count="8">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Snapshots" displayName="Snapshots" ref="A1:K2" headerRowCount="1">
+  <autoFilter ref="A1:K2"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="Snapshot date"/>
     <tableColumn id="2" name="URN"/>
-    <tableColumn id="3" name="Overall members"/>
-    <tableColumn id="4" name="Rep count"/>
-    <tableColumn id="5" name="Workforce headcount"/>
-    <tableColumn id="6" name="Voted"/>
-    <tableColumn id="7" name="Volunteers"/>
-    <tableColumn id="8" name="WP conversations"/>
+    <tableColumn id="3" name="Membership (total)"/>
+    <tableColumn id="4" name="Membership (teachers)"/>
+    <tableColumn id="5" name="Membership (leadership)"/>
+    <tableColumn id="6" name="Membership (support)"/>
+    <tableColumn id="7" name="Headcount (total)"/>
+    <tableColumn id="8" name="Headcount (teachers)"/>
+    <tableColumn id="9" name="Headcount (leadership)"/>
+    <tableColumn id="10" name="Headcount (support)"/>
+    <tableColumn id="11" name="Rep count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="SchoolGeo" displayName="SchoolGeo" ref="A1:D2" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Reconciliations" displayName="Reconciliations" ref="A1:H2" headerRowCount="1">
+  <autoFilter ref="A1:H2"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Anomaly type"/>
+    <tableColumn id="3" name="Key (URN or workplace code)"/>
+    <tableColumn id="4" name="Action"/>
+    <tableColumn id="5" name="Target key"/>
+    <tableColumn id="6" name="Note"/>
+    <tableColumn id="7" name="Decided by"/>
+    <tableColumn id="8" name="Decided date"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="SchoolGeo" displayName="SchoolGeo" ref="A1:D2" headerRowCount="1">
   <autoFilter ref="A1:D2"/>
   <tableColumns count="4">
     <tableColumn id="1" name="URN"/>
@@ -222,42 +269,82 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="SourceHistoricalDisputes" displayName="SourceHistoricalDisputes" ref="A1:F2" headerRowCount="1">
-  <autoFilter ref="A1:F2"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="School year"/>
-    <tableColumn id="2" name="Employer/school"/>
-    <tableColumn id="3" name="Branch"/>
-    <tableColumn id="4" name="RO/SRO responsible"/>
-    <tableColumn id="5" name="Ballot summary"/>
-    <tableColumn id="6" name="Notes"/>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceStratum" displayName="SourceStratum" ref="A1:K2" headerRowCount="1">
+  <autoFilter ref="A1:K2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="Workplace code"/>
+    <tableColumn id="2" name="Workplace name"/>
+    <tableColumn id="3" name="Headcount (total)"/>
+    <tableColumn id="4" name="Headcount (teachers)"/>
+    <tableColumn id="5" name="Headcount (leadership)"/>
+    <tableColumn id="6" name="Headcount (support)"/>
+    <tableColumn id="7" name="Membership (total)"/>
+    <tableColumn id="8" name="Membership (teachers)"/>
+    <tableColumn id="9" name="Membership (leadership)"/>
+    <tableColumn id="10" name="Membership (support)"/>
+    <tableColumn id="11" name="Export date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceWorkforce" displayName="SourceWorkforce" ref="A1:J2" headerRowCount="1">
-  <autoFilter ref="A1:J2"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="URN"/>
-    <tableColumn id="2" name="School name"/>
-    <tableColumn id="3" name="LA (borough)"/>
-    <tableColumn id="4" name="School type"/>
-    <tableColumn id="5" name="Workforce headcount"/>
-    <tableColumn id="6" name="All teachers"/>
-    <tableColumn id="7" name="Classroom teachers"/>
-    <tableColumn id="8" name="Leadership teachers"/>
-    <tableColumn id="9" name="All support staff"/>
-    <tableColumn id="10" name="Teaching assistants"/>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcePayDashboard" displayName="SourcePayDashboard" ref="A1:U2" headerRowCount="1">
+  <autoFilter ref="A1:U2"/>
+  <tableColumns count="21">
+    <tableColumn id="1" name="Workplace code"/>
+    <tableColumn id="2" name="Workplace name"/>
+    <tableColumn id="3" name="Rep count"/>
+    <tableColumn id="4" name="Members voted (2026 indicative)"/>
+    <tableColumn id="5" name="Members voted (2025 indicative)"/>
+    <tableColumn id="6" name="Members voted (2024 indicative)"/>
+    <tableColumn id="7" name="Turnout (2026 indicative)"/>
+    <tableColumn id="8" name="Volunteers"/>
+    <tableColumn id="9" name="WP conversations"/>
+    <tableColumn id="10" name="Active SEVs"/>
+    <tableColumn id="11" name="Rep recruited volunteer"/>
+    <tableColumn id="12" name="Joined community"/>
+    <tableColumn id="13" name="Completed activate action"/>
+    <tableColumn id="14" name="Agreed to briefing"/>
+    <tableColumn id="15" name="Hold a meeting"/>
+    <tableColumn id="16" name="Needs support"/>
+    <tableColumn id="17" name="Pledged to vote"/>
+    <tableColumn id="18" name="Branch name"/>
+    <tableColumn id="19" name="District name"/>
+    <tableColumn id="20" name="Region name"/>
+    <tableColumn id="21" name="Import date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WCtoURN" displayName="WCtoURN" ref="A1:B2" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourceWorkforceSurvey" displayName="SourceWorkforceSurvey" ref="A1:O2" headerRowCount="1">
+  <autoFilter ref="A1:O2"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="URN"/>
+    <tableColumn id="2" name="Headcount (third party)"/>
+    <tableColumn id="3" name="Annual turnover (total)"/>
+    <tableColumn id="4" name="Pupil:teacher ratio (qualified)"/>
+    <tableColumn id="5" name="Average mean pay"/>
+    <tableColumn id="6" name="Vacancies"/>
+    <tableColumn id="7" name="Average sick days"/>
+    <tableColumn id="8" name="School name"/>
+    <tableColumn id="9" name="LA (borough)"/>
+    <tableColumn id="10" name="School type"/>
+    <tableColumn id="11" name="All teachers"/>
+    <tableColumn id="12" name="Classroom teachers"/>
+    <tableColumn id="13" name="Leadership teachers"/>
+    <tableColumn id="14" name="All support staff"/>
+    <tableColumn id="15" name="Teaching assistants"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="WCtoURN" displayName="WCtoURN" ref="A1:B2" headerRowCount="1">
   <autoFilter ref="A1:B2"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Workplace code"/>
@@ -267,40 +354,20 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourceNEUDashboard" displayName="SourceNEUDashboard" ref="A1:V2" headerRowCount="1">
-  <autoFilter ref="A1:V2"/>
-  <tableColumns count="22">
-    <tableColumn id="1" name="Workplace code"/>
-    <tableColumn id="2" name="Workplace name"/>
-    <tableColumn id="3" name="Overall members"/>
-    <tableColumn id="4" name="Voted"/>
-    <tableColumn id="5" name="Turnout"/>
-    <tableColumn id="6" name="Rep count"/>
-    <tableColumn id="7" name="Branch name"/>
-    <tableColumn id="8" name="District name"/>
-    <tableColumn id="9" name="Region name"/>
-    <tableColumn id="10" name="Volunteers"/>
-    <tableColumn id="11" name="WP conversations"/>
-    <tableColumn id="12" name="Rep recruited volunteer"/>
-    <tableColumn id="13" name="Joined community"/>
-    <tableColumn id="14" name="Completed activate action"/>
-    <tableColumn id="15" name="Agreed to briefing"/>
-    <tableColumn id="16" name="2025 indicative voted"/>
-    <tableColumn id="17" name="2024 indicative voted"/>
-    <tableColumn id="18" name="Hold a meeting"/>
-    <tableColumn id="19" name="Needs support"/>
-    <tableColumn id="20" name="Pledged to vote"/>
-    <tableColumn id="21" name="Active SEVs"/>
-    <tableColumn id="22" name="Import date"/>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="MatAliases" displayName="MatAliases" ref="A1:B3" headerRowCount="1">
+  <autoFilter ref="A1:B3"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Alias (as it appears in source data)"/>
+    <tableColumn id="2" name="Canonical MAT name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FieldNotes" displayName="FieldNotes" ref="A1:G3" headerRowCount="1">
-  <autoFilter ref="A1:G3"/>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="FieldNotes" displayName="FieldNotes" ref="A1:G2" headerRowCount="1">
+  <autoFilter ref="A1:G2"/>
   <tableColumns count="7">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -314,63 +381,44 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DisputeTracker" displayName="DisputeTracker" ref="A1:P2" headerRowCount="1">
-  <autoFilter ref="A1:P2"/>
-  <tableColumns count="16">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="DisputeTracker" displayName="DisputeTracker" ref="A1:V2" headerRowCount="1">
+  <autoFilter ref="A1:V2"/>
+  <tableColumns count="22">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Employer"/>
     <tableColumn id="3" name="MAT"/>
     <tableColumn id="4" name="Branch"/>
-    <tableColumn id="5" name="Live"/>
-    <tableColumn id="6" name="# Schools"/>
-    <tableColumn id="7" name="ROR/IO"/>
-    <tableColumn id="8" name="Staff responsible"/>
-    <tableColumn id="9" name="Issues"/>
-    <tableColumn id="10" name="Date indicative opens"/>
-    <tableColumn id="11" name="Indicative %"/>
-    <tableColumn id="12" name="Membership at indicative"/>
-    <tableColumn id="13" name="Formal ballot %"/>
-    <tableColumn id="14" name="Date of resolution"/>
-    <tableColumn id="15" name="Outcome (RAG)"/>
-    <tableColumn id="16" name="Total strike days"/>
+    <tableColumn id="5" name="Affected URNs"/>
+    <tableColumn id="6" name="Live"/>
+    <tableColumn id="7" name="Dispute lead (IO/ROR/SIO)"/>
+    <tableColumn id="8" name="Dispute lead (name)"/>
+    <tableColumn id="9" name="Dispute issues"/>
+    <tableColumn id="10" name="Indicative opens (date)"/>
+    <tableColumn id="11" name="Trade dispute letter (doc link)"/>
+    <tableColumn id="12" name="Resolved prior to action (y/n)"/>
+    <tableColumn id="13" name="Indicative %"/>
+    <tableColumn id="14" name="Membership at indicative"/>
+    <tableColumn id="15" name="Formal ballot request (doc link)"/>
+    <tableColumn id="16" name="Notice of formal ballot (doc link)"/>
+    <tableColumn id="17" name="Formal %"/>
+    <tableColumn id="18" name="Notice of strike dates (doc link)"/>
+    <tableColumn id="19" name="Date of resolution"/>
+    <tableColumn id="20" name="Outcome (RAG)"/>
+    <tableColumn id="21" name="Total strike days"/>
+    <tableColumn id="22" name="End of dispute report (doc link)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="BranchFacts" displayName="BranchFacts" ref="A1:C33" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="BranchFacts" displayName="BranchFacts" ref="A1:C33" headerRowCount="1">
   <autoFilter ref="A1:C33"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Branch"/>
     <tableColumn id="2" name="Is project branch?"/>
     <tableColumn id="3" name="Reps trained since start"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="MatFacts" displayName="MatFacts" ref="A1:C2" headerRowCount="1">
-  <autoFilter ref="A1:C2"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="MAT"/>
-    <tableColumn id="2" name="Is target MAT?"/>
-    <tableColumn id="3" name="Rep committee exists?"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Meetings" displayName="Meetings" ref="A1:D2" headerRowCount="1">
-  <autoFilter ref="A1:D2"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Date"/>
-    <tableColumn id="3" name="URN"/>
-    <tableColumn id="4" name="Logged by"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -665,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -854,6 +902,13 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -868,7 +923,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MAT</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Is target MAT?</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Rep committee exists?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Oscar Romero</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>COLA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Haberdashers</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Compass Eko</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Orchard Hill</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Note: One row per MAT you're tracking. Use the canonical name — see MatAliases if a trust appears under more than one name in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>URN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Logged by</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>m1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>100097</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Organiser</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Written by the app from a school's page. Branch and project meeting counts derive from this — do not keep a separate tally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -933,7 +1213,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Append-only log of reps recruited, written one-click by the app. Distinct from reps TRAINED, which is still a manual figure on BranchFacts.</t>
+          <t>Note: Written by the app from a school's page. Distinct from reps TRAINED, which is still a manual figure on BranchFacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
@@ -945,23 +1232,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -977,32 +1267,47 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Overall members</t>
+          <t>Membership (total)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Membership (teachers)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Membership (leadership)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Membership (support)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Headcount (total)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Headcount (teachers)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Headcount (leadership)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Headcount (support)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Rep count</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Workforce headcount</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Voted</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Volunteers</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>WP conversations</t>
         </is>
       </c>
     </row>
@@ -1019,25 +1324,41 @@
         <v>19</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="H2" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Append-only weekly capture, written automatically by the app. NEVER edit or delete past rows — this is the only record of how things looked at the time, and it cannot be reconstructed.</t>
+          <t>Note: Written automatically by the app. NEVER edit or delete past rows — this is the only record of how things looked at the time and it cannot be reconstructed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
@@ -1049,13 +1370,143 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Anomaly type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Key (URN or workplace code)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Decided by</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Decided date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>rc1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>unmatched-workplace-code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>WP999999</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>100097</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE — code belonged to the school before it converted</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Organiser</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Written by the app's Anomalies page. Append-only: superseding a decision means adding a newer row, not editing an old one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"link,successor,accept,exclude"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1105,7 +1556,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Cached postcode-&gt;coordinates lookups for the map view. Populated once by the app; safe to delete rows to force a re-lookup.</t>
+          <t>Note: Populated by the Map page's 'Locate missing schools' button. Safe to delete rows to force a re-lookup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
@@ -1117,91 +1575,137 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>School year</t>
+          <t>Workplace code</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Employer/school</t>
+          <t>Workplace name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Headcount (total)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RO/SRO responsible</t>
+          <t>Headcount (teachers)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ballot summary</t>
+          <t>Headcount (leadership)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Headcount (support)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Membership (total)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Membership (teachers)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Membership (leadership)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Membership (support)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Export date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2022-23</t>
+          <t>WP020292</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE School</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Harrow</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE Officer</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>56% turnout, 43% Yes</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Kept for institutional memory — not read by the app.</t>
+          <t>EXAMPLE Rachel McMillan Nursery School</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Reference only, not read by the app or kept up to date automatically.</t>
+          <t>Note: Paste your Stratum export here (the 'Full Membership List for Stats purposes' report). This is the primary source for headcount and membership — the workforce survey's headcount is treated as a third-party cross-check. Not edited by the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
@@ -1213,121 +1717,233 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>URN</t>
+          <t>Workplace code</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>School name</t>
+          <t>Workplace name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>LA (borough)</t>
+          <t>Rep count</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>School type</t>
+          <t>Members voted (2026 indicative)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Workforce headcount</t>
+          <t>Members voted (2025 indicative)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>All teachers</t>
+          <t>Members voted (2024 indicative)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Classroom teachers</t>
+          <t>Turnout (2026 indicative)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Leadership teachers</t>
+          <t>Volunteers</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>All support staff</t>
+          <t>WP conversations</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Teaching assistants</t>
+          <t>Active SEVs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Rep recruited volunteer</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Joined community</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Completed activate action</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Agreed to briefing</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Hold a meeting</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Needs support</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Pledged to vote</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Branch name</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>District name</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Region name</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Import date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>100097</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WP020292</t>
+        </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>EXAMPLE Rachel McMillan Nursery School</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Greenwich State Education</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Greenwich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>LA maintained nursery</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>15</v>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Paste your DfE School Workforce Census export here. Not edited by the app.</t>
+          <t>Note: Paste your NEU Pay Dashboard export here. Membership and headcount now come from Stratum instead — this source covers ballots, engagement and rep count. Not edited by the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1955,191 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>URN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Headcount (third party)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Annual turnover (total)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pupil:teacher ratio (qualified)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Average mean pay</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Vacancies</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Average sick days</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>School name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LA (borough)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>School type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>All teachers</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Classroom teachers</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Leadership teachers</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>All support staff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Teaching assistants</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>100097</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>41200</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Rachel McMillan Nursery School</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Greenwich</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>LA maintained nursery</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Paste your DfE School Workforce Census export here. Headcount here is a THIRD-PARTY figure — Stratum is the source used for density. Not edited by the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1377,7 +2171,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Maps NEU workplace codes to DfE URNs. Not edited by the app.</t>
+          <t>Note: Maps NEU workplace codes to DfE URNs. Codes that don't map appear on the Anomalies page — resolve them there rather than editing rollups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
@@ -1389,235 +2190,66 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="27" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Workplace code</t>
+          <t>Alias (as it appears in source data)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Workplace name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Overall members</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Voted</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Turnout</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Rep count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Branch name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>District name</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Region name</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Volunteers</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>WP conversations</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Rep recruited volunteer</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Joined community</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Completed activate action</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Agreed to briefing</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>2025 indicative voted</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>2024 indicative voted</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Hold a meeting</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Needs support</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Pledged to vote</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Active SEVs</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Import date</t>
+          <t>Canonical MAT name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WP020292</t>
+          <t>Compass Partnership of Schools</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE Rachel McMillan Nursery School</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Greenwich State Education</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Greenwich</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Note: Paste your NEU membership/organising system export here. Not edited by the app.</t>
+          <t>Compass Eko</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EKO Trust</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Compass Eko</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Note: One row per alternative name. E.g. 'Compass Partnership of Schools' and 'EKO Trust' both -&gt; 'Compass Eko'. Prevents a merged trust appearing as two MATs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
@@ -1629,7 +2261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1721,53 +2353,23 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>n2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Greenwich</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE — how to log a branch note</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>This is how you write a note on a whole branch. Subject = the branch/borough name.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE Author</t>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Edited by the app's Field notes page. Subject is a URN for School-level notes, or the branch/MAT name otherwise.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Note: Edited by the app's Field notes page. Subject is a URN for School-level notes, or the branch/MAT name otherwise.</t>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"School,MAT,Branch"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1778,31 +2380,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1828,62 +2436,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Affected URNs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Live</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t># Schools</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ROR/IO</t>
+          <t>Dispute lead (IO/ROR/SIO)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Staff responsible</t>
+          <t>Dispute lead (name)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>Dispute issues</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Date indicative opens</t>
+          <t>Indicative opens (date)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Trade dispute letter (doc link)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Resolved prior to action (y/n)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Indicative %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Membership at indicative</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Formal ballot %</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Formal ballot request (doc link)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Notice of formal ballot (doc link)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Formal %</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Notice of strike dates (doc link)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Date of resolution</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Outcome (RAG)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Total strike days</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>End of dispute report (doc link)</t>
         </is>
       </c>
     </row>
@@ -1910,12 +2548,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>100097</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>ROR</t>
@@ -1936,35 +2576,55 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Edited by the app's Dispute tracker page. Issues is a comma-separated list; Indicative %/Formal ballot % are fractions (0.72 = 72%).</t>
+          <t>Note: Edited by the app's Dispute tracker page. 'Affected URNs' is a comma-separated list chosen by searching for schools; the number of schools derives from it. Percentages are fractions (0.72 = 72%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ROR,IO,SIO"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Red,Amber,Green"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1975,13 +2635,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2149,7 +2809,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2224,7 +2884,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2239,7 +2899,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2284,7 +2944,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2464,7 +3124,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2489,13 +3149,20 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Note: One row per London borough/branch. 'Is project branch?' controls whether it counts toward the dashboard's headline KPIs. School meetings are no longer counted here — they come from the Meetings table.</t>
+          <t>Note: One row per London borough. 'Is project branch?' controls the dashboard's headline KPIs and the star in list views. School meetings are NOT counted here — they come from the Meetings table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2504,147 +3171,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MAT</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Is target MAT?</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Rep committee exists?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE MAT</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Note: Add a row per MAT you're tracking. Edit directly in Excel whenever a new MAT enters the project.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>URN</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Logged by</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>m1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>100097</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE Organiser</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Note: Append-only log of school meetings, written one-click by the app. Branch and project meeting counts are derived from this — do not keep a separate tally.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
+++ b/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
@@ -19,9 +19,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MatFacts" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meetings" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RepsRecruited" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshots" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliations" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchoolGeo" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RepCommittees" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshots" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliations" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchoolGeo" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -220,7 +221,21 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Snapshots" displayName="Snapshots" ref="A1:K2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="RepCommittees" displayName="RepCommittees" ref="A1:E2" headerRowCount="1">
+  <autoFilter ref="A1:E2"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="MAT"/>
+    <tableColumn id="3" name="Committee exists"/>
+    <tableColumn id="4" name="Effective from"/>
+    <tableColumn id="5" name="Logged by"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Snapshots" displayName="Snapshots" ref="A1:K2" headerRowCount="1">
   <autoFilter ref="A1:K2"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Snapshot date"/>
@@ -239,8 +254,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Reconciliations" displayName="Reconciliations" ref="A1:H2" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Reconciliations" displayName="Reconciliations" ref="A1:H2" headerRowCount="1">
   <autoFilter ref="A1:H2"/>
   <tableColumns count="8">
     <tableColumn id="1" name="ID"/>
@@ -256,8 +271,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="SchoolGeo" displayName="SchoolGeo" ref="A1:D2" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="SchoolGeo" displayName="SchoolGeo" ref="A1:D2" headerRowCount="1">
   <autoFilter ref="A1:D2"/>
   <tableColumns count="4">
     <tableColumn id="1" name="URN"/>
@@ -1238,6 +1253,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MAT</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Committee exists</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Effective from</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Logged by</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>rcm1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Trust</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE Organiser</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Note: Written by the app from a MAT's page. The current status is the most recent row by effective date; MatFacts 'Rep committee exists' is the fallback for trusts with no rows yet. NEVER edit or delete past rows — they are the only record of when a committee was in place, and that cannot be reconstructed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1370,7 +1477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1500,7 +1607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
+++ b/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceGIAS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceStratum" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourcePayDashboard" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceWorkforceSurvey" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCtoURN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MatAliases" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldNotes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DisputeTracker" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BranchFacts" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MatFacts" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meetings" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RepsRecruited" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RepCommittees" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshots" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliations" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchoolGeo" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SourceGIAS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SourceStratum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SourcePayDashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SourceWorkforceSurvey" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="WCtoURN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MatAliases" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FieldNotes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DisputeTracker" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BranchFacts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MatFacts" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Meetings" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="RepCommittees" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Snapshots" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Reconciliations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SchoolGeo" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -194,34 +193,21 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Meetings" displayName="Meetings" ref="A1:D2" headerRowCount="1">
-  <autoFilter ref="A1:D2"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Date"/>
-    <tableColumn id="3" name="URN"/>
-    <tableColumn id="4" name="Logged by"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="RepsRecruited" displayName="RepsRecruited" ref="A1:E2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Meetings" displayName="Meetings" ref="A1:E2" headerRowCount="1">
   <autoFilter ref="A1:E2"/>
   <tableColumns count="5">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
     <tableColumn id="3" name="URN"/>
-    <tableColumn id="4" name="Rep name"/>
-    <tableColumn id="5" name="Logged by"/>
+    <tableColumn id="4" name="Logged by"/>
+    <tableColumn id="5" name="Attendees"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="RepCommittees" displayName="RepCommittees" ref="A1:E2" headerRowCount="1">
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="RepCommittees" displayName="RepCommittees" ref="A1:E2" headerRowCount="1">
   <autoFilter ref="A1:E2"/>
   <tableColumns count="5">
     <tableColumn id="1" name="ID"/>
@@ -234,8 +220,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Snapshots" displayName="Snapshots" ref="A1:K2" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Snapshots" displayName="Snapshots" ref="A1:K2" headerRowCount="1">
   <autoFilter ref="A1:K2"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Snapshot date"/>
@@ -254,8 +240,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Reconciliations" displayName="Reconciliations" ref="A1:H2" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Reconciliations" displayName="Reconciliations" ref="A1:H2" headerRowCount="1">
   <autoFilter ref="A1:H2"/>
   <tableColumns count="8">
     <tableColumn id="1" name="ID"/>
@@ -271,8 +257,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="SchoolGeo" displayName="SchoolGeo" ref="A1:D2" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="SchoolGeo" displayName="SchoolGeo" ref="A1:D2" headerRowCount="1">
   <autoFilter ref="A1:D2"/>
   <tableColumns count="4">
     <tableColumn id="1" name="URN"/>
@@ -285,9 +271,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceStratum" displayName="SourceStratum" ref="A1:K2" headerRowCount="1">
-  <autoFilter ref="A1:K2"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourceStratum" displayName="SourceStratum" ref="A1:L2" headerRowCount="1">
+  <autoFilter ref="A1:L2"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Workplace code"/>
     <tableColumn id="2" name="Workplace name"/>
     <tableColumn id="3" name="Headcount (total)"/>
@@ -298,37 +284,37 @@
     <tableColumn id="8" name="Membership (teachers)"/>
     <tableColumn id="9" name="Membership (leadership)"/>
     <tableColumn id="10" name="Membership (support)"/>
-    <tableColumn id="11" name="Export date"/>
+    <tableColumn id="11" name="Rep count"/>
+    <tableColumn id="12" name="Export date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcePayDashboard" displayName="SourcePayDashboard" ref="A1:U2" headerRowCount="1">
-  <autoFilter ref="A1:U2"/>
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcePayDashboard" displayName="SourcePayDashboard" ref="A1:T2" headerRowCount="1">
+  <autoFilter ref="A1:T2"/>
+  <tableColumns count="20">
     <tableColumn id="1" name="Workplace code"/>
     <tableColumn id="2" name="Workplace name"/>
-    <tableColumn id="3" name="Rep count"/>
-    <tableColumn id="4" name="Members voted (2026 indicative)"/>
-    <tableColumn id="5" name="Members voted (2025 indicative)"/>
-    <tableColumn id="6" name="Members voted (2024 indicative)"/>
-    <tableColumn id="7" name="Turnout (2026 indicative)"/>
-    <tableColumn id="8" name="Volunteers"/>
-    <tableColumn id="9" name="WP conversations"/>
-    <tableColumn id="10" name="Active SEVs"/>
-    <tableColumn id="11" name="Rep recruited volunteer"/>
-    <tableColumn id="12" name="Joined community"/>
-    <tableColumn id="13" name="Completed activate action"/>
-    <tableColumn id="14" name="Agreed to briefing"/>
-    <tableColumn id="15" name="Hold a meeting"/>
-    <tableColumn id="16" name="Needs support"/>
-    <tableColumn id="17" name="Pledged to vote"/>
-    <tableColumn id="18" name="Branch name"/>
-    <tableColumn id="19" name="District name"/>
-    <tableColumn id="20" name="Region name"/>
-    <tableColumn id="21" name="Import date"/>
+    <tableColumn id="3" name="Members voted (2026 indicative)"/>
+    <tableColumn id="4" name="Members voted (2025 indicative)"/>
+    <tableColumn id="5" name="Members voted (2024 indicative)"/>
+    <tableColumn id="6" name="Turnout (2026 indicative)"/>
+    <tableColumn id="7" name="Volunteers"/>
+    <tableColumn id="8" name="WP conversations"/>
+    <tableColumn id="9" name="Active SEVs"/>
+    <tableColumn id="10" name="Rep recruited volunteer"/>
+    <tableColumn id="11" name="Joined community"/>
+    <tableColumn id="12" name="Completed activate action"/>
+    <tableColumn id="13" name="Agreed to briefing"/>
+    <tableColumn id="14" name="Hold a meeting"/>
+    <tableColumn id="15" name="Needs support"/>
+    <tableColumn id="16" name="Pledged to vote"/>
+    <tableColumn id="17" name="Branch name"/>
+    <tableColumn id="18" name="District name"/>
+    <tableColumn id="19" name="Region name"/>
+    <tableColumn id="20" name="Import date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -1084,85 +1070,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>URN</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Logged by</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>m1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>100097</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>EXAMPLE Organiser</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Note: Written by the app from a school's page. Branch and project meeting counts derive from this — do not keep a separate tally.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Column order must match data-dictionary/dictionary.json — the app reads columns by position.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1191,24 +1098,24 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Rep name</t>
+          <t>Logged by</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Logged by</t>
+          <t>Attendees</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>r1</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -1216,19 +1123,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE Rep</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
           <t>EXAMPLE Organiser</t>
         </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Written by the app from a school's page. Distinct from reps TRAINED, which is still a manual figure on BranchFacts.</t>
+          <t>Note: Written by the app from a school's page. Branch and project meeting counts derive from this — do not keep a separate tally. Attendees is the organiser's count on the day and may be approximate; it is blank on rows logged before that column existed.</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1339,7 +1244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1477,7 +1382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1607,7 +1512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1688,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1701,7 +1606,8 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1757,6 +1663,11 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Rep count</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Export date</t>
         </is>
       </c>
@@ -1796,7 +1707,10 @@
       <c r="J2" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
@@ -1805,7 +1719,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Paste your Stratum export here (the 'Full Membership List for Stats purposes' report). This is the primary source for headcount and membership — the workforce survey's headcount is treated as a third-party cross-check. Not edited by the app.</t>
+          <t>Note: Paste your Stratum export here (the 'Full Membership List for Stats purposes' report). This is the primary source for headcount, membership and rep count — the workforce survey's headcount is treated as a third-party cross-check. Not edited by the app.</t>
         </is>
       </c>
     </row>
@@ -1830,30 +1744,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1869,95 +1782,90 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Rep count</t>
+          <t>Members voted (2026 indicative)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Members voted (2026 indicative)</t>
+          <t>Members voted (2025 indicative)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Members voted (2025 indicative)</t>
+          <t>Members voted (2024 indicative)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Members voted (2024 indicative)</t>
+          <t>Turnout (2026 indicative)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Turnout (2026 indicative)</t>
+          <t>Volunteers</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Volunteers</t>
+          <t>WP conversations</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>WP conversations</t>
+          <t>Active SEVs</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Active SEVs</t>
+          <t>Rep recruited volunteer</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Rep recruited volunteer</t>
+          <t>Joined community</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Joined community</t>
+          <t>Completed activate action</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Completed activate action</t>
+          <t>Agreed to briefing</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Agreed to briefing</t>
+          <t>Hold a meeting</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Hold a meeting</t>
+          <t>Needs support</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Needs support</t>
+          <t>Pledged to vote</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Pledged to vote</t>
+          <t>Branch name</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Branch name</t>
+          <t>District name</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>District name</t>
+          <t>Region name</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Region name</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Import date</t>
         </is>
@@ -1975,66 +1883,63 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>9</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Greenwich State Education</t>
+        </is>
+      </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Greenwich State Education</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>London</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
@@ -2043,7 +1948,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Note: Paste your NEU Pay Dashboard export here. Membership and headcount now come from Stratum instead — this source covers ballots, engagement and rep count. Not edited by the app.</t>
+          <t>Note: Paste your NEU Pay Dashboard export here. Membership and headcount come from Stratum, and so does the rep count — this source covers ballots and engagement. Not edited by the app.</t>
         </is>
       </c>
     </row>

--- a/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
+++ b/london-mapping/workbook-template/London_Project_Mapping_template.xlsx
@@ -73,11 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -181,12 +183,13 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="MatFacts" displayName="MatFacts" ref="A1:C6" headerRowCount="1">
-  <autoFilter ref="A1:C6"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="MatFacts" displayName="MatFacts" ref="A1:D6" headerRowCount="1">
+  <autoFilter ref="A1:D6"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="MAT"/>
     <tableColumn id="2" name="Is target MAT?"/>
     <tableColumn id="3" name="Rep committee exists?"/>
+    <tableColumn id="4" name="Companies House number"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -924,12 +927,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" style="4" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -948,6 +952,11 @@
           <t>Rep committee exists?</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Companies House number</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -965,6 +974,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -982,6 +992,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -999,6 +1010,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1016,6 +1028,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1033,11 +1046,12 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D6" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Note: One row per MAT you're tracking. Use the canonical name — see MatAliases if a trust appears under more than one name in the source data.</t>
+          <t>Note: One row per MAT you're tracking. Use the canonical name — see MatAliases if a trust appears under more than one name in the source data. 'Companies House number' is only used to link out to the Bargaining Dashboard — it is formatted as text so leading zeros survive.</t>
         </is>
       </c>
     </row>
